--- a/rapporten/prijsrapport-2026-04-14.xlsx
+++ b/rapporten/prijsrapport-2026-04-14.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="105">
   <si>
     <t>Product</t>
   </si>
@@ -49,195 +49,159 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Dorall Twilight Wilderness - Herenparfum eau de toilette - 100 ml</t>
-  </si>
-  <si>
-    <t>6291012874381</t>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494225</t>
+  </si>
+  <si>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493860</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494263</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816691</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816677</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816653</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494270</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055494232</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493891</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816714</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816615</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493211</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816790</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816639</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493884</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816837</t>
+  </si>
+  <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816813</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493853</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
+  </si>
+  <si>
+    <t>8721055493877</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493198</t>
+  </si>
+  <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8721055493228</t>
+  </si>
+  <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658370505</t>
+  </si>
+  <si>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
+    <t>8715658370062</t>
+  </si>
+  <si>
+    <t>Omerta - Express sensualite Captive - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658999027</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
   </si>
   <si>
-    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494225</t>
-  </si>
-  <si>
-    <t>Minimarkt W&amp;M</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493860</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494263</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816691</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816677</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816653</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494270</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055494232</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493891</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816714</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816615</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493211</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816790</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816639</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493884</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816837</t>
-  </si>
-  <si>
-    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816813</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493853</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493877</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493198</t>
-  </si>
-  <si>
-    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>8721055493228</t>
-  </si>
-  <si>
-    <t>Creation Lamis Pluton for men Eau de Toilette</t>
-  </si>
-  <si>
-    <t>6291012005969</t>
-  </si>
-  <si>
-    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370505</t>
-  </si>
-  <si>
-    <t>Bliksma Retail B.V.</t>
-  </si>
-  <si>
-    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658370062</t>
-  </si>
-  <si>
-    <t>NG Homme for Men Eau de Toilette 100 ml</t>
-  </si>
-  <si>
-    <t>8718421831425</t>
-  </si>
-  <si>
-    <t>Omerta - Invasion Third Dimension - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658380368</t>
-  </si>
-  <si>
-    <t>Omerta - Candy Puff - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380801</t>
-  </si>
-  <si>
-    <t>Creation Lamis Ruler Giftset</t>
-  </si>
-  <si>
-    <t>6291012002678</t>
-  </si>
-  <si>
-    <t>Omerta - Ma Merveilleuse - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658997443</t>
-  </si>
-  <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
   </si>
   <si>
@@ -362,18 +326,6 @@
   </si>
   <si>
     <t>8715658380580</t>
-  </si>
-  <si>
-    <t>Omerta - Conclude Oud Orient Perfection - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370550</t>
-  </si>
-  <si>
-    <t>Bubble Bliss Fantastic Flamingo - Parfum Set Van 6 Stuks - Eau de Parfum Voor Kinderen - 6x15ml</t>
-  </si>
-  <si>
-    <t>8721055493914</t>
   </si>
 </sst>
 </file>
@@ -765,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -838,19 +790,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>12.76</v>
+        <v>5.25</v>
       </c>
       <c r="D3" s="1">
-        <v>12.33</v>
+        <v>4.99</v>
       </c>
       <c r="E3" s="1">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>12.33</v>
+        <v>4.99</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -873,7 +825,7 @@
         <v>0.26</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
         <v>4.99</v>
@@ -884,11 +836,11 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" s="1">
         <v>5.25</v>
       </c>
@@ -899,7 +851,7 @@
         <v>0.26</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
         <v>4.99</v>
@@ -910,11 +862,11 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
       <c r="C6" s="1">
         <v>5.25</v>
       </c>
@@ -925,7 +877,7 @@
         <v>0.26</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
         <v>4.99</v>
@@ -936,11 +888,11 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="1">
         <v>5.25</v>
       </c>
@@ -951,7 +903,7 @@
         <v>0.26</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
         <v>4.99</v>
@@ -962,11 +914,11 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
       <c r="C8" s="1">
         <v>5.25</v>
       </c>
@@ -977,7 +929,7 @@
         <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
         <v>4.99</v>
@@ -988,11 +940,11 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
       <c r="C9" s="1">
         <v>5.25</v>
       </c>
@@ -1003,7 +955,7 @@
         <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1">
         <v>4.99</v>
@@ -1014,11 +966,11 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
       <c r="C10" s="1">
         <v>5.25</v>
       </c>
@@ -1029,7 +981,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1040,11 +992,11 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" s="1">
         <v>5.25</v>
       </c>
@@ -1055,7 +1007,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1066,11 +1018,11 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
       <c r="C12" s="1">
         <v>5.25</v>
       </c>
@@ -1081,7 +1033,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1092,11 +1044,11 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
       <c r="C13" s="1">
         <v>5.25</v>
       </c>
@@ -1107,7 +1059,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1118,11 +1070,11 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
       <c r="C14" s="1">
         <v>5.25</v>
       </c>
@@ -1133,7 +1085,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1144,11 +1096,11 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
       <c r="C15" s="1">
         <v>5.25</v>
       </c>
@@ -1159,7 +1111,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1170,11 +1122,11 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" s="1">
         <v>5.25</v>
       </c>
@@ -1185,7 +1137,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1196,11 +1148,11 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>42</v>
       </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
       <c r="C17" s="1">
         <v>5.25</v>
       </c>
@@ -1211,7 +1163,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1222,11 +1174,11 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
         <v>44</v>
       </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
       <c r="C18" s="1">
         <v>5.25</v>
       </c>
@@ -1237,7 +1189,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1248,11 +1200,11 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
         <v>46</v>
       </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
       <c r="C19" s="1">
         <v>5.25</v>
       </c>
@@ -1263,7 +1215,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1274,11 +1226,11 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
       <c r="C20" s="1">
         <v>5.25</v>
       </c>
@@ -1289,7 +1241,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1300,11 +1252,11 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
         <v>50</v>
       </c>
-      <c r="B21" t="s">
-        <v>51</v>
-      </c>
       <c r="C21" s="1">
         <v>5.25</v>
       </c>
@@ -1315,7 +1267,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1326,11 +1278,11 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
         <v>52</v>
       </c>
-      <c r="B22" t="s">
-        <v>53</v>
-      </c>
       <c r="C22" s="1">
         <v>5.25</v>
       </c>
@@ -1341,7 +1293,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1352,11 +1304,11 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
         <v>54</v>
       </c>
-      <c r="B23" t="s">
-        <v>55</v>
-      </c>
       <c r="C23" s="1">
         <v>5.25</v>
       </c>
@@ -1367,7 +1319,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1378,25 +1330,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
         <v>56</v>
       </c>
-      <c r="B24" t="s">
-        <v>57</v>
-      </c>
       <c r="C24" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D24" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E24" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G24" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
@@ -1410,19 +1362,19 @@
         <v>59</v>
       </c>
       <c r="C25" s="1">
-        <v>11.75</v>
+        <v>9.99</v>
       </c>
       <c r="D25" s="1">
-        <v>11.5</v>
+        <v>9.75</v>
       </c>
       <c r="E25" s="1">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="G25" s="1">
-        <v>11.5</v>
+        <v>9.75</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -1436,19 +1388,19 @@
         <v>61</v>
       </c>
       <c r="C26" s="1">
-        <v>9.99</v>
+        <v>11.95</v>
       </c>
       <c r="D26" s="1">
-        <v>9.75</v>
+        <v>11.87</v>
       </c>
       <c r="E26" s="1">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="F26" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="1">
-        <v>9.75</v>
+        <v>11.87</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -1465,16 +1417,16 @@
         <v>9.99</v>
       </c>
       <c r="D27" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="E27" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G27" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
@@ -1488,19 +1440,19 @@
         <v>66</v>
       </c>
       <c r="C28" s="1">
-        <v>11.69</v>
+        <v>9.99</v>
       </c>
       <c r="D28" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E28" s="1">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="G28" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -1514,19 +1466,19 @@
         <v>68</v>
       </c>
       <c r="C29" s="1">
-        <v>11.67</v>
+        <v>9.99</v>
       </c>
       <c r="D29" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E29" s="1">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="G29" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1540,19 +1492,19 @@
         <v>70</v>
       </c>
       <c r="C30" s="1">
-        <v>11.97</v>
+        <v>9.99</v>
       </c>
       <c r="D30" s="1">
-        <v>11.82</v>
+        <v>9.95</v>
       </c>
       <c r="E30" s="1">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="G30" s="1">
-        <v>11.82</v>
+        <v>9.95</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1566,19 +1518,19 @@
         <v>72</v>
       </c>
       <c r="C31" s="1">
-        <v>11.59</v>
+        <v>9.99</v>
       </c>
       <c r="D31" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E31" s="1">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="G31" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -1592,19 +1544,19 @@
         <v>74</v>
       </c>
       <c r="C32" s="1">
-        <v>11.57</v>
+        <v>9.99</v>
       </c>
       <c r="D32" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="E32" s="1">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="G32" s="1">
-        <v>11.5</v>
+        <v>9.95</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1627,7 +1579,7 @@
         <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G33" s="1">
         <v>9.95</v>
@@ -1653,7 +1605,7 @@
         <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G34" s="1">
         <v>9.95</v>
@@ -1679,7 +1631,7 @@
         <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G35" s="1">
         <v>9.95</v>
@@ -1705,7 +1657,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1731,7 +1683,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1757,7 +1709,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1783,7 +1735,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1809,7 +1761,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1835,7 +1787,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1861,7 +1813,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1887,7 +1839,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1913,7 +1865,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1939,7 +1891,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1965,7 +1917,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -1991,220 +1943,12 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D48" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E48" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F48" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D49" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E49" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F49" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D50" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E50" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F50" t="s">
-        <v>62</v>
-      </c>
-      <c r="G50" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>111</v>
-      </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D51" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F51" t="s">
-        <v>62</v>
-      </c>
-      <c r="G51" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D52" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E52" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F52" t="s">
-        <v>62</v>
-      </c>
-      <c r="G52" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D53" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" t="s">
-        <v>118</v>
-      </c>
-      <c r="C54" s="1">
-        <v>11.75</v>
-      </c>
-      <c r="D54" s="1">
-        <v>11.72</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="F54" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="1">
-        <v>11.72</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>119</v>
-      </c>
-      <c r="B55" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="1">
-        <v>15.95</v>
-      </c>
-      <c r="D55" s="1">
-        <v>15.93</v>
-      </c>
-      <c r="E55" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="F55" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" s="1">
-        <v>15.93</v>
-      </c>
-      <c r="H55" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-14.xlsx
+++ b/rapporten/prijsrapport-2026-04-14.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="102">
   <si>
     <t>Product</t>
   </si>
@@ -191,15 +191,6 @@
   </si>
   <si>
     <t>8715658370062</t>
-  </si>
-  <si>
-    <t>Omerta - Express sensualite Captive - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658999027</t>
-  </si>
-  <si>
-    <t>Koopjesfun.nl</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -717,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1388,19 +1379,19 @@
         <v>61</v>
       </c>
       <c r="C26" s="1">
-        <v>11.95</v>
+        <v>9.99</v>
       </c>
       <c r="D26" s="1">
-        <v>11.87</v>
+        <v>9.95</v>
       </c>
       <c r="E26" s="1">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G26" s="1">
-        <v>11.87</v>
+        <v>9.95</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -1408,10 +1399,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
         <v>63</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
       </c>
       <c r="C27" s="1">
         <v>9.99</v>
@@ -1434,10 +1425,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
         <v>65</v>
-      </c>
-      <c r="B28" t="s">
-        <v>66</v>
       </c>
       <c r="C28" s="1">
         <v>9.99</v>
@@ -1460,10 +1451,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
         <v>67</v>
-      </c>
-      <c r="B29" t="s">
-        <v>68</v>
       </c>
       <c r="C29" s="1">
         <v>9.99</v>
@@ -1486,10 +1477,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
         <v>69</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
       </c>
       <c r="C30" s="1">
         <v>9.99</v>
@@ -1512,10 +1503,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
         <v>71</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
       </c>
       <c r="C31" s="1">
         <v>9.99</v>
@@ -1538,10 +1529,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
         <v>73</v>
-      </c>
-      <c r="B32" t="s">
-        <v>74</v>
       </c>
       <c r="C32" s="1">
         <v>9.99</v>
@@ -1564,10 +1555,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
         <v>75</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
       </c>
       <c r="C33" s="1">
         <v>9.99</v>
@@ -1590,10 +1581,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
         <v>77</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
       </c>
       <c r="C34" s="1">
         <v>9.99</v>
@@ -1616,10 +1607,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
         <v>79</v>
-      </c>
-      <c r="B35" t="s">
-        <v>80</v>
       </c>
       <c r="C35" s="1">
         <v>9.99</v>
@@ -1642,10 +1633,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
         <v>81</v>
-      </c>
-      <c r="B36" t="s">
-        <v>82</v>
       </c>
       <c r="C36" s="1">
         <v>9.99</v>
@@ -1668,10 +1659,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
         <v>83</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
       </c>
       <c r="C37" s="1">
         <v>9.99</v>
@@ -1694,10 +1685,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
         <v>85</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
       </c>
       <c r="C38" s="1">
         <v>9.99</v>
@@ -1720,10 +1711,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
         <v>87</v>
-      </c>
-      <c r="B39" t="s">
-        <v>88</v>
       </c>
       <c r="C39" s="1">
         <v>9.99</v>
@@ -1746,10 +1737,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
         <v>89</v>
-      </c>
-      <c r="B40" t="s">
-        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>9.99</v>
@@ -1772,10 +1763,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
         <v>91</v>
-      </c>
-      <c r="B41" t="s">
-        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>9.99</v>
@@ -1798,10 +1789,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
         <v>93</v>
-      </c>
-      <c r="B42" t="s">
-        <v>94</v>
       </c>
       <c r="C42" s="1">
         <v>9.99</v>
@@ -1824,10 +1815,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
         <v>95</v>
-      </c>
-      <c r="B43" t="s">
-        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>9.99</v>
@@ -1850,10 +1841,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
         <v>97</v>
-      </c>
-      <c r="B44" t="s">
-        <v>98</v>
       </c>
       <c r="C44" s="1">
         <v>9.99</v>
@@ -1876,10 +1867,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
         <v>99</v>
-      </c>
-      <c r="B45" t="s">
-        <v>100</v>
       </c>
       <c r="C45" s="1">
         <v>9.99</v>
@@ -1902,11 +1893,11 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" t="s">
         <v>101</v>
       </c>
-      <c r="B46" t="s">
-        <v>102</v>
-      </c>
       <c r="C46" s="1">
         <v>9.99</v>
       </c>
@@ -1923,32 +1914,6 @@
         <v>9.95</v>
       </c>
       <c r="H46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" t="s">
-        <v>104</v>
-      </c>
-      <c r="C47" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D47" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E47" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
-      <c r="G47" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H47" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-14.xlsx
+++ b/rapporten/prijsrapport-2026-04-14.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="101">
   <si>
     <t>Product</t>
   </si>
@@ -106,12 +106,6 @@
     <t>8721055493891</t>
   </si>
   <si>
-    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816714</t>
-  </si>
-  <si>
     <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
   </si>
   <si>
@@ -130,12 +124,6 @@
     <t>7640158816790</t>
   </si>
   <si>
-    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816639</t>
-  </si>
-  <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
   </si>
   <si>
@@ -176,6 +164,15 @@
   </si>
   <si>
     <t>8721055493228</t>
+  </si>
+  <si>
+    <t>Catsuit Man parfum - Heren eau de toilette met munt, lavendel en bergamot</t>
+  </si>
+  <si>
+    <t>8719992723812</t>
+  </si>
+  <si>
+    <t>Koopjesfun.nl</t>
   </si>
   <si>
     <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
@@ -708,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1275,19 +1272,19 @@
         <v>52</v>
       </c>
       <c r="C22" s="1">
-        <v>5.25</v>
+        <v>15.75</v>
       </c>
       <c r="D22" s="1">
-        <v>4.99</v>
+        <v>15.5</v>
       </c>
       <c r="E22" s="1">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="G22" s="1">
-        <v>4.99</v>
+        <v>15.5</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1295,25 +1292,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D23" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E23" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="G23" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -1321,10 +1318,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1">
         <v>9.99</v>
@@ -1336,7 +1333,7 @@
         <v>0.24</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G24" s="1">
         <v>9.75</v>
@@ -1347,25 +1344,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1">
         <v>9.99</v>
       </c>
       <c r="D25" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="E25" s="1">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="1">
-        <v>9.75</v>
+        <v>9.95</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -1373,10 +1370,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1">
         <v>9.99</v>
@@ -1388,7 +1385,7 @@
         <v>0.04</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G26" s="1">
         <v>9.95</v>
@@ -1399,10 +1396,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1">
         <v>9.99</v>
@@ -1414,7 +1411,7 @@
         <v>0.04</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" s="1">
         <v>9.95</v>
@@ -1425,10 +1422,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1">
         <v>9.99</v>
@@ -1440,7 +1437,7 @@
         <v>0.04</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G28" s="1">
         <v>9.95</v>
@@ -1451,10 +1448,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1">
         <v>9.99</v>
@@ -1466,7 +1463,7 @@
         <v>0.04</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G29" s="1">
         <v>9.95</v>
@@ -1477,10 +1474,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1">
         <v>9.99</v>
@@ -1492,7 +1489,7 @@
         <v>0.04</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G30" s="1">
         <v>9.95</v>
@@ -1503,10 +1500,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1">
         <v>9.99</v>
@@ -1518,7 +1515,7 @@
         <v>0.04</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G31" s="1">
         <v>9.95</v>
@@ -1529,10 +1526,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1">
         <v>9.99</v>
@@ -1544,7 +1541,7 @@
         <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G32" s="1">
         <v>9.95</v>
@@ -1555,10 +1552,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1">
         <v>9.99</v>
@@ -1570,7 +1567,7 @@
         <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G33" s="1">
         <v>9.95</v>
@@ -1581,10 +1578,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1">
         <v>9.99</v>
@@ -1596,7 +1593,7 @@
         <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G34" s="1">
         <v>9.95</v>
@@ -1607,10 +1604,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1">
         <v>9.99</v>
@@ -1622,7 +1619,7 @@
         <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G35" s="1">
         <v>9.95</v>
@@ -1633,10 +1630,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1">
         <v>9.99</v>
@@ -1648,7 +1645,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1659,10 +1656,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1">
         <v>9.99</v>
@@ -1674,7 +1671,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1685,10 +1682,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1">
         <v>9.99</v>
@@ -1700,7 +1697,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1711,10 +1708,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1">
         <v>9.99</v>
@@ -1726,7 +1723,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1737,10 +1734,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>9.99</v>
@@ -1752,7 +1749,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1763,10 +1760,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>9.99</v>
@@ -1778,7 +1775,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1789,10 +1786,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1">
         <v>9.99</v>
@@ -1804,7 +1801,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1815,10 +1812,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>9.99</v>
@@ -1830,7 +1827,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1841,10 +1838,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1">
         <v>9.99</v>
@@ -1856,7 +1853,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1867,10 +1864,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
         <v>9.99</v>
@@ -1882,38 +1879,12 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
       </c>
       <c r="H45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>100</v>
-      </c>
-      <c r="B46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D46" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E46" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F46" t="s">
-        <v>57</v>
-      </c>
-      <c r="G46" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H46" t="s">
         <v>11</v>
       </c>
     </row>
